--- a/database/supabase/templates/template_import_books.xlsx
+++ b/database/supabase/templates/template_import_books.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,17 +27,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Segoe UI"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
-    <font>
-      <name val="Segoe UI"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -46,18 +42,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001A4FA3"/>
-        <bgColor rgb="001A4FA3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00009688"/>
-        <bgColor rgb="00009688"/>
+        <fgColor rgb="00366092"/>
+        <bgColor rgb="00366092"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -65,20 +55,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -445,20 +452,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="65" customWidth="1" min="2" max="2"/>
+    <col width="75" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="47" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>isbn</t>
@@ -500,213 +507,953 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>978-0134685991</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Effective Java</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+          <t>9780134685991</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Effective Java (3rd Edition)</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Joshua Bloch</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Addison-Wesley</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="n">
+        <v>2018</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>850000</v>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Computer Science</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Textbook, Coding</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Textbook,Coding,Reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>978-0596009205</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Head First Java</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Kathy Sierra</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+          <t>9780132350884</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Clean Code</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Robert C. Martin</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Prentice Hall</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>2008</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>650000</v>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Textbook,Coding</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>9780201633610</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Design Patterns: Elements of Reusable Object-Oriented Software</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Erich Gamma, Richard Helm, Ralph Johnson, John Vlissides</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Addison-Wesley</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>1994</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>950000</v>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Reference,Theoretical</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>9781119560822</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Corporate Finance (12th Edition)</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Stephen Ross, Randolph Westerfield, Jeffrey Jaffe</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Wiley</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Economics &amp; Finance</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Textbook,CaseStudy</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>9780321356680</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Algorithms (4th Edition)</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Robert Sedgewick, Kevin Wayne</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Addison-Wesley</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>2011</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>900000</v>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Textbook,Coding,Theoretical</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>9780073523323</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Macroeconomics (9th Edition)</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>N. Gregory Mankiw</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Worth Publishers</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>800000</v>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Economics &amp; Finance</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Textbook,Theoretical</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>9780199232741</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Introduction to Politics</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Robert Garner, Peter Ferdinand, Stephanie Lawson</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Oxford University Press</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>2016</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>550000</v>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Politics &amp; International Relations</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Introduction,Textbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>9781449331818</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Designing Data-Intensive Applications</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Martin Kleppmann</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>O'Reilly Media</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>30.00</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="E9" s="2" t="n">
+        <v>2017</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>Computer Science</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Textbook, Introduction</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>978-0262033848</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Introduction to Algorithms</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Thomas H. Cormen</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Reference,Advanced</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>9780132145374</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence: A Modern Approach (3rd Edition)</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Stuart Russell, Peter Norvig</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Pearson</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>2010</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Textbook,AI_Driven,Advanced</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>9780321573513</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Introduction to Electrodynamics (4th Edition)</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>David J. Griffiths</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Pearson</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>2012</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>750000</v>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Textbook,Theoretical</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>9780134093413</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Campbell Biology (11th Edition)</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Lisa A. Urry, Michael L. Cain</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Pearson</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>2016</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Biology &amp; Ecology</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Textbook,Reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>9780470503201</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Introduction to Physics (9th Edition)</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>John D. Cutnell, Kenneth W. Johnson</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Wiley</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>2012</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>700000</v>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Introduction,Textbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>9780078021558</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Organic Chemistry (9th Edition)</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Francis Carey, Robert Giuliano</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>McGraw-Hill Education</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>2013</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Textbook,Experimental</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>9780136006633</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Microbiology: An Introduction (10th Edition)</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Gerard J. Tortora, Berdell R. Funke</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Pearson</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>2009</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>1420000</v>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Biology &amp; Ecology,Medicine &amp; Health Sciences</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Textbook,LabManual</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>9780470646151</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Principles of Anatomy and Physiology (13th Edition)</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Gerard J. Tortora, Bryan H. Derrickson</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Wiley</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>2011</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Medicine &amp; Health Sciences</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Textbook,Reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>9781285057903</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Introduction to Business (5th Edition)</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Jeff Madura</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Cengage Learning</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>2013</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>600000</v>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Business Administration</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Introduction,Textbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>9780133098754</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Marketing Management (15th Edition)</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Philip Kotler, Kevin Lane Keller</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Pearson</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>1150000</v>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Business Administration</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Textbook,CaseStudy,Strategic</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>9781133312789</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>General, Organic, and Biological Chemistry</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>H. Stephen Stoker</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Cengage Learning</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>980000</v>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Chemistry,Pharmacy &amp; Biochemistry</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Textbook,LabManual</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>9780199571123</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Introduction to Law</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Jaap Hage, Bram Akkermans</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Springer</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>2014</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>670000</v>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Law &amp; Legal Studies</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Introduction,Textbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>9781305073036</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Principles of Psychology</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>S. Marc Breedlove</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Oxford University Press</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>850000</v>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Psychology</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Textbook,Behavioral</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>9780321838964</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Designing the User Interface (6th Edition)</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Ben Shneiderman, Catherine Plaisant</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Pearson</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>2016</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>930000</v>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Computer Science,Arts &amp; Design</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Reference,Visual_Design</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>9780133914641</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering (10th Edition)</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Ian Sommerville</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Pearson</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>950000</v>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Textbook,Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>9781491950296</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Kafka: The Definitive Guide</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Neha Narkhede, Gwen Shapira, Todd Palino</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>O'Reilly Media</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>2017</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>650000</v>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Reference,Advanced</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>9781501257285</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Soft Skills: The software developer's life manual</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>John Sonmez</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Manning Publications</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>2014</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>450000</v>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Soft Skills</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Reference,Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>9780073523859</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Introduction to Algorithms (3rd Edition)</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Thomas H. Cormen, Charles E. Leiserson, Ronald L. Rivest, Clifford Stein</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>MIT Press</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>85.00</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="E26" s="2" t="n">
+        <v>2009</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>Computer Science</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Textbook, Advanced</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>978-0132350884</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Clean Code</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Robert C. Martin</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Prentice Hall</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>42.50</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Computer Science</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Reference, Coding</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>978-1492056300</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Designing Data-Intensive Applications</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Martin Kleppmann</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>O'Reilly Media</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Computer Science</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Monograph, BigData</t>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Textbook,Theoretical,Advanced</t>
         </is>
       </c>
     </row>
@@ -721,130 +1468,1303 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>isbn</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>barcode</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>location</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>978-0134685991</t>
+          <t>9780134685991</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>BC-EJ-001</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Shelf-A1</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
+          <t>BC9780134685991-01</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Kệ CS-5991-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>978-0134685991</t>
+          <t>9780134685991</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>BC-EJ-002</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Shelf-A1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
+          <t>BC9780134685991-02</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Kệ CS-5991-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>978-0596009205</t>
+          <t>9780134685991</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>BC-HFJ-001</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Shelf-A1</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1">
+          <t>BC9780134685991-03</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Kệ CS-5991-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>978-0262033848</t>
+          <t>9780132350884</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>BC-ITA-001</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Shelf-A2</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
+          <t>BC9780132350884-01</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Kệ CS-0884-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>978-0132350884</t>
+          <t>9780132350884</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>BC-CC-001</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Shelf-A2</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
+          <t>BC9780132350884-02</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Kệ CS-0884-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>978-1492056300</t>
+          <t>9780132350884</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>BC-DDIA-001</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Shelf-B1</t>
+          <t>BC9780132350884-03</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Kệ CS-0884-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>9780201633610</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>BC9780201633610-01</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Kệ CS-3610-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>9780201633610</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>BC9780201633610-02</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Kệ CS-3610-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>9780201633610</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>BC9780201633610-03</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Kệ CS-3610-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>9781119560822</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>BC9781119560822-01</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Kệ GEN-0822-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>9781119560822</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>BC9781119560822-02</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Kệ GEN-0822-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>9781119560822</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>BC9781119560822-03</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Kệ GEN-0822-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>9780321356680</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>BC9780321356680-01</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Kệ CS-6680-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>9780321356680</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>BC9780321356680-02</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Kệ CS-6680-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>9780321356680</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>BC9780321356680-03</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Kệ CS-6680-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>9780073523323</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>BC9780073523323-01</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Kệ GEN-3323-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>9780073523323</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>BC9780073523323-02</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Kệ GEN-3323-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>9780073523323</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>BC9780073523323-03</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Kệ GEN-3323-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>9780199232741</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>BC9780199232741-01</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Kệ GEN-2741-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>9780199232741</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>BC9780199232741-02</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Kệ GEN-2741-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>9780199232741</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>BC9780199232741-03</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Kệ GEN-2741-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>9781449331818</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>BC9781449331818-01</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Kệ CS-1818-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>9781449331818</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>BC9781449331818-02</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Kệ CS-1818-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>9781449331818</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>BC9781449331818-03</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Kệ CS-1818-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>9780132145374</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>BC9780132145374-01</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Kệ CS-5374-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>9780132145374</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>BC9780132145374-02</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Kệ CS-5374-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>9780132145374</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>BC9780132145374-03</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Kệ CS-5374-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>9780321573513</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>BC9780321573513-01</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Kệ GEN-3513-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>9780321573513</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>BC9780321573513-02</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Kệ GEN-3513-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>9780321573513</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>BC9780321573513-03</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Kệ GEN-3513-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>9780134093413</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>BC9780134093413-01</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Kệ GEN-3413-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>9780134093413</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>BC9780134093413-02</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Kệ GEN-3413-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>9780134093413</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>BC9780134093413-03</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Kệ GEN-3413-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>9780470503201</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>BC9780470503201-01</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Kệ GEN-3201-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>9780470503201</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>BC9780470503201-02</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Kệ GEN-3201-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>9780470503201</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>BC9780470503201-03</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Kệ GEN-3201-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>9780078021558</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>BC9780078021558-01</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Kệ GEN-1558-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>9780078021558</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>BC9780078021558-02</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Kệ GEN-1558-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>9780078021558</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>BC9780078021558-03</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Kệ GEN-1558-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>9780136006633</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>BC9780136006633-01</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Kệ GEN-6633-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>9780136006633</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>BC9780136006633-02</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Kệ GEN-6633-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>9780136006633</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>BC9780136006633-03</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Kệ GEN-6633-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>9780470646151</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>BC9780470646151-01</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Kệ GEN-6151-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>9780470646151</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>BC9780470646151-02</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Kệ GEN-6151-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>9780470646151</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>BC9780470646151-03</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Kệ GEN-6151-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>9781285057903</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>BC9781285057903-01</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Kệ GEN-7903-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>9781285057903</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>BC9781285057903-02</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Kệ GEN-7903-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>9781285057903</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>BC9781285057903-03</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Kệ GEN-7903-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>9780133098754</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>BC9780133098754-01</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Kệ GEN-8754-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>9780133098754</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>BC9780133098754-02</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Kệ GEN-8754-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>9780133098754</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>BC9780133098754-03</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Kệ GEN-8754-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>9781133312789</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>BC9781133312789-01</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Kệ GEN-2789-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>9781133312789</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>BC9781133312789-02</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>Kệ GEN-2789-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>9781133312789</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>BC9781133312789-03</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>Kệ GEN-2789-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>9780199571123</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>BC9780199571123-01</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Kệ GEN-1123-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>9780199571123</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>BC9780199571123-02</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>Kệ GEN-1123-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>9780199571123</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>BC9780199571123-03</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Kệ GEN-1123-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>9781305073036</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>BC9781305073036-01</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>Kệ GEN-3036-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>9781305073036</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>BC9781305073036-02</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Kệ GEN-3036-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>9781305073036</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>BC9781305073036-03</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>Kệ GEN-3036-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>9780321838964</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>BC9780321838964-01</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Kệ CS-8964-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>9780321838964</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>BC9780321838964-02</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>Kệ CS-8964-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>9780321838964</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>BC9780321838964-03</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>Kệ CS-8964-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>9780133914641</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>BC9780133914641-01</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>Kệ CS-4641-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>9780133914641</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>BC9780133914641-02</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>Kệ CS-4641-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>9780133914641</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>BC9780133914641-03</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>Kệ CS-4641-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>9781491950296</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>BC9781491950296-01</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>Kệ CS-0296-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>9781491950296</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>BC9781491950296-02</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>Kệ CS-0296-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>9781491950296</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>BC9781491950296-03</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>Kệ CS-0296-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>9781501257285</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>BC9781501257285-01</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>Kệ GEN-7285-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>9781501257285</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>BC9781501257285-02</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Kệ GEN-7285-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>9781501257285</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>BC9781501257285-03</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>Kệ GEN-7285-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>9780073523859</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>BC9780073523859-01</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Kệ CS-3859-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>9780073523859</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>BC9780073523859-02</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>Kệ CS-3859-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>9780073523859</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>BC9780073523859-03</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>Kệ CS-3859-3</t>
         </is>
       </c>
     </row>

--- a/database/supabase/templates/template_import_books.xlsx
+++ b/database/supabase/templates/template_import_books.xlsx
@@ -1468,7 +1468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C76"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1530,17 +1530,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>9780134685991</t>
+          <t>9780132350884</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>BC9780134685991-03</t>
+          <t>BC9780132350884-01</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Kệ CS-5991-3</t>
+          <t>Kệ CS-0884-1</t>
         </is>
       </c>
     </row>
@@ -1552,1219 +1552,794 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>BC9780132350884-01</t>
+          <t>BC9780132350884-02</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Kệ CS-0884-1</t>
+          <t>Kệ CS-0884-2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>9780132350884</t>
+          <t>9780201633610</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>BC9780132350884-02</t>
+          <t>BC9780201633610-01</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Kệ CS-0884-2</t>
+          <t>Kệ CS-3610-1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>9780132350884</t>
+          <t>9780201633610</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>BC9780132350884-03</t>
+          <t>BC9780201633610-02</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Kệ CS-0884-3</t>
+          <t>Kệ CS-3610-2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>9780201633610</t>
+          <t>9781119560822</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>BC9780201633610-01</t>
+          <t>BC9781119560822-01</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Kệ CS-3610-1</t>
+          <t>Kệ GEN-0822-1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>9780201633610</t>
+          <t>9781119560822</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>BC9780201633610-02</t>
+          <t>BC9781119560822-02</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Kệ CS-3610-2</t>
+          <t>Kệ GEN-0822-2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>9780201633610</t>
+          <t>9780321356680</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>BC9780201633610-03</t>
+          <t>BC9780321356680-01</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Kệ CS-3610-3</t>
+          <t>Kệ CS-6680-1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>9781119560822</t>
+          <t>9780321356680</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>BC9781119560822-01</t>
+          <t>BC9780321356680-02</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Kệ GEN-0822-1</t>
+          <t>Kệ CS-6680-2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>9781119560822</t>
+          <t>9780073523323</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>BC9781119560822-02</t>
+          <t>BC9780073523323-01</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Kệ GEN-0822-2</t>
+          <t>Kệ GEN-3323-1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>9781119560822</t>
+          <t>9780073523323</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>BC9781119560822-03</t>
+          <t>BC9780073523323-02</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Kệ GEN-0822-3</t>
+          <t>Kệ GEN-3323-2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>9780321356680</t>
+          <t>9780199232741</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>BC9780321356680-01</t>
+          <t>BC9780199232741-01</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Kệ CS-6680-1</t>
+          <t>Kệ GEN-2741-1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>9780321356680</t>
+          <t>9780199232741</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>BC9780321356680-02</t>
+          <t>BC9780199232741-02</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Kệ CS-6680-2</t>
+          <t>Kệ GEN-2741-2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>9780321356680</t>
+          <t>9781449331818</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>BC9780321356680-03</t>
+          <t>BC9781449331818-01</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Kệ CS-6680-3</t>
+          <t>Kệ CS-1818-1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>9780073523323</t>
+          <t>9781449331818</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>BC9780073523323-01</t>
+          <t>BC9781449331818-02</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Kệ GEN-3323-1</t>
+          <t>Kệ CS-1818-2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>9780073523323</t>
+          <t>9780132145374</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>BC9780073523323-02</t>
+          <t>BC9780132145374-01</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Kệ GEN-3323-2</t>
+          <t>Kệ CS-5374-1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>9780073523323</t>
+          <t>9780132145374</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>BC9780073523323-03</t>
+          <t>BC9780132145374-02</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Kệ GEN-3323-3</t>
+          <t>Kệ CS-5374-2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>9780199232741</t>
+          <t>9780321573513</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>BC9780199232741-01</t>
+          <t>BC9780321573513-01</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Kệ GEN-2741-1</t>
+          <t>Kệ GEN-3513-1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>9780199232741</t>
+          <t>9780321573513</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>BC9780199232741-02</t>
+          <t>BC9780321573513-02</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Kệ GEN-2741-2</t>
+          <t>Kệ GEN-3513-2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>9780199232741</t>
+          <t>9780134093413</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>BC9780199232741-03</t>
+          <t>BC9780134093413-01</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Kệ GEN-2741-3</t>
+          <t>Kệ GEN-3413-1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>9781449331818</t>
+          <t>9780134093413</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>BC9781449331818-01</t>
+          <t>BC9780134093413-02</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Kệ CS-1818-1</t>
+          <t>Kệ GEN-3413-2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>9781449331818</t>
+          <t>9780470503201</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>BC9781449331818-02</t>
+          <t>BC9780470503201-01</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Kệ CS-1818-2</t>
+          <t>Kệ GEN-3201-1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>9781449331818</t>
+          <t>9780470503201</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>BC9781449331818-03</t>
+          <t>BC9780470503201-02</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Kệ CS-1818-3</t>
+          <t>Kệ GEN-3201-2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>9780132145374</t>
+          <t>9780078021558</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>BC9780132145374-01</t>
+          <t>BC9780078021558-01</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Kệ CS-5374-1</t>
+          <t>Kệ GEN-1558-1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>9780132145374</t>
+          <t>9780078021558</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>BC9780132145374-02</t>
+          <t>BC9780078021558-02</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Kệ CS-5374-2</t>
+          <t>Kệ GEN-1558-2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>9780132145374</t>
+          <t>9780136006633</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>BC9780132145374-03</t>
+          <t>BC9780136006633-01</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Kệ CS-5374-3</t>
+          <t>Kệ GEN-6633-1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>9780321573513</t>
+          <t>9780136006633</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>BC9780321573513-01</t>
+          <t>BC9780136006633-02</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Kệ GEN-3513-1</t>
+          <t>Kệ GEN-6633-2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>9780321573513</t>
+          <t>9780470646151</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>BC9780321573513-02</t>
+          <t>BC9780470646151-01</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Kệ GEN-3513-2</t>
+          <t>Kệ GEN-6151-1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>9780321573513</t>
+          <t>9780470646151</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>BC9780321573513-03</t>
+          <t>BC9780470646151-02</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Kệ GEN-3513-3</t>
+          <t>Kệ GEN-6151-2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>9780134093413</t>
+          <t>9781285057903</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>BC9780134093413-01</t>
+          <t>BC9781285057903-01</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Kệ GEN-3413-1</t>
+          <t>Kệ GEN-7903-1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>9780134093413</t>
+          <t>9781285057903</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>BC9780134093413-02</t>
+          <t>BC9781285057903-02</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Kệ GEN-3413-2</t>
+          <t>Kệ GEN-7903-2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>9780134093413</t>
+          <t>9780133098754</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>BC9780134093413-03</t>
+          <t>BC9780133098754-01</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Kệ GEN-3413-3</t>
+          <t>Kệ GEN-8754-1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>9780470503201</t>
+          <t>9780133098754</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>BC9780470503201-01</t>
+          <t>BC9780133098754-02</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Kệ GEN-3201-1</t>
+          <t>Kệ GEN-8754-2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>9780470503201</t>
+          <t>9781133312789</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>BC9780470503201-02</t>
+          <t>BC9781133312789-01</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Kệ GEN-3201-2</t>
+          <t>Kệ GEN-2789-1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>9780470503201</t>
+          <t>9781133312789</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>BC9780470503201-03</t>
+          <t>BC9781133312789-02</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Kệ GEN-3201-3</t>
+          <t>Kệ GEN-2789-2</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>9780078021558</t>
+          <t>9780199571123</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>BC9780078021558-01</t>
+          <t>BC9780199571123-01</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Kệ GEN-1558-1</t>
+          <t>Kệ GEN-1123-1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>9780078021558</t>
+          <t>9780199571123</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>BC9780078021558-02</t>
+          <t>BC9780199571123-02</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Kệ GEN-1558-2</t>
+          <t>Kệ GEN-1123-2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>9780078021558</t>
+          <t>9781305073036</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>BC9780078021558-03</t>
+          <t>BC9781305073036-01</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Kệ GEN-1558-3</t>
+          <t>Kệ GEN-3036-1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>9780136006633</t>
+          <t>9781305073036</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>BC9780136006633-01</t>
+          <t>BC9781305073036-02</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Kệ GEN-6633-1</t>
+          <t>Kệ GEN-3036-2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>9780136006633</t>
+          <t>9780321838964</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>BC9780136006633-02</t>
+          <t>BC9780321838964-01</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Kệ GEN-6633-2</t>
+          <t>Kệ CS-8964-1</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>9780136006633</t>
+          <t>9780321838964</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>BC9780136006633-03</t>
+          <t>BC9780321838964-02</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Kệ GEN-6633-3</t>
+          <t>Kệ CS-8964-2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>9780470646151</t>
+          <t>9780133914641</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>BC9780470646151-01</t>
+          <t>BC9780133914641-01</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Kệ GEN-6151-1</t>
+          <t>Kệ CS-4641-1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>9780470646151</t>
+          <t>9780133914641</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>BC9780470646151-02</t>
+          <t>BC9780133914641-02</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Kệ GEN-6151-2</t>
+          <t>Kệ CS-4641-2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>9780470646151</t>
+          <t>9781491950296</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>BC9780470646151-03</t>
+          <t>BC9781491950296-01</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Kệ GEN-6151-3</t>
+          <t>Kệ CS-0296-1</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>9781285057903</t>
+          <t>9781491950296</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>BC9781285057903-01</t>
+          <t>BC9781491950296-02</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Kệ GEN-7903-1</t>
+          <t>Kệ CS-0296-2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>9781285057903</t>
+          <t>9781501257285</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>BC9781285057903-02</t>
+          <t>BC9781501257285-01</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Kệ GEN-7903-2</t>
+          <t>Kệ GEN-7285-1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>9781285057903</t>
+          <t>9781501257285</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>BC9781285057903-03</t>
+          <t>BC9781501257285-02</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Kệ GEN-7903-3</t>
+          <t>Kệ GEN-7285-2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>9780133098754</t>
+          <t>9780073523859</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>BC9780133098754-01</t>
+          <t>BC9780073523859-01</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Kệ GEN-8754-1</t>
+          <t>Kệ CS-3859-1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>9780133098754</t>
+          <t>9780073523859</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>BC9780133098754-02</t>
+          <t>BC9780073523859-02</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Kệ GEN-8754-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>9780133098754</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>BC9780133098754-03</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>Kệ GEN-8754-3</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>9781133312789</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>BC9781133312789-01</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>Kệ GEN-2789-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>9781133312789</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>BC9781133312789-02</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>Kệ GEN-2789-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>9781133312789</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>BC9781133312789-03</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>Kệ GEN-2789-3</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>9780199571123</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>BC9780199571123-01</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t>Kệ GEN-1123-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>9780199571123</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>BC9780199571123-02</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>Kệ GEN-1123-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>9780199571123</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>BC9780199571123-03</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
-        <is>
-          <t>Kệ GEN-1123-3</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>9781305073036</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>BC9781305073036-01</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>Kệ GEN-3036-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>9781305073036</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>BC9781305073036-02</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>Kệ GEN-3036-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>9781305073036</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>BC9781305073036-03</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t>Kệ GEN-3036-3</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>9780321838964</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>BC9780321838964-01</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>Kệ CS-8964-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>9780321838964</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>BC9780321838964-02</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t>Kệ CS-8964-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>9780321838964</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>BC9780321838964-03</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>Kệ CS-8964-3</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>9780133914641</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>BC9780133914641-01</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t>Kệ CS-4641-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>9780133914641</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>BC9780133914641-02</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="inlineStr">
-        <is>
-          <t>Kệ CS-4641-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>9780133914641</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>BC9780133914641-03</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>Kệ CS-4641-3</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>9781491950296</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>BC9781491950296-01</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t>Kệ CS-0296-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>9781491950296</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>BC9781491950296-02</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="inlineStr">
-        <is>
-          <t>Kệ CS-0296-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>9781491950296</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>BC9781491950296-03</t>
-        </is>
-      </c>
-      <c r="C70" s="3" t="inlineStr">
-        <is>
-          <t>Kệ CS-0296-3</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>9781501257285</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>BC9781501257285-01</t>
-        </is>
-      </c>
-      <c r="C71" s="3" t="inlineStr">
-        <is>
-          <t>Kệ GEN-7285-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>9781501257285</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>BC9781501257285-02</t>
-        </is>
-      </c>
-      <c r="C72" s="3" t="inlineStr">
-        <is>
-          <t>Kệ GEN-7285-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>9781501257285</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>BC9781501257285-03</t>
-        </is>
-      </c>
-      <c r="C73" s="3" t="inlineStr">
-        <is>
-          <t>Kệ GEN-7285-3</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>9780073523859</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>BC9780073523859-01</t>
-        </is>
-      </c>
-      <c r="C74" s="3" t="inlineStr">
-        <is>
-          <t>Kệ CS-3859-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>9780073523859</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>BC9780073523859-02</t>
-        </is>
-      </c>
-      <c r="C75" s="3" t="inlineStr">
-        <is>
           <t>Kệ CS-3859-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>9780073523859</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>BC9780073523859-03</t>
-        </is>
-      </c>
-      <c r="C76" s="3" t="inlineStr">
-        <is>
-          <t>Kệ CS-3859-3</t>
         </is>
       </c>
     </row>

--- a/database/supabase/templates/template_import_books.xlsx
+++ b/database/supabase/templates/template_import_books.xlsx
@@ -84,7 +84,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -541,7 +541,7 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Textbook,Coding,Reference</t>
+          <t>Textbook;Coding;Reference</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Textbook,Coding</t>
+          <t>Textbook;Coding</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Reference,Theoretical</t>
+          <t>Reference;Theoretical</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Textbook,CaseStudy</t>
+          <t>Textbook;CaseStudy</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Textbook,Coding,Theoretical</t>
+          <t>Textbook;Coding;Theoretical</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Textbook,Theoretical</t>
+          <t>Textbook;Theoretical</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Introduction,Textbook</t>
+          <t>Introduction;Textbook</t>
         </is>
       </c>
     </row>
@@ -807,7 +807,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Reference,Advanced</t>
+          <t>Reference;Advanced</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Textbook,AI_Driven,Advanced</t>
+          <t>Textbook;AI_Driven;Advanced</t>
         </is>
       </c>
     </row>
@@ -883,7 +883,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Textbook,Theoretical</t>
+          <t>Textbook;Theoretical</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Textbook,Reference</t>
+          <t>Textbook;Reference</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Introduction,Textbook</t>
+          <t>Introduction;Textbook</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Textbook,Experimental</t>
+          <t>Textbook;Experimental</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Biology &amp; Ecology,Medicine &amp; Health Sciences</t>
+          <t>Biology &amp; Ecology;Medicine &amp; Health Sciences</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Textbook,LabManual</t>
+          <t>Textbook;LabManual</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Textbook,Reference</t>
+          <t>Textbook;Reference</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Introduction,Textbook</t>
+          <t>Introduction;Textbook</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Textbook,CaseStudy,Strategic</t>
+          <t>Textbook;CaseStudy;Strategic</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Chemistry,Pharmacy &amp; Biochemistry</t>
+          <t>Chemistry;Pharmacy &amp; Biochemistry</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Textbook,LabManual</t>
+          <t>Textbook;LabManual</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Introduction,Textbook</t>
+          <t>Introduction;Textbook</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Textbook,Behavioral</t>
+          <t>Textbook;Behavioral</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Computer Science,Arts &amp; Design</t>
+          <t>Computer Science;Arts &amp; Design</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Reference,Visual_Design</t>
+          <t>Reference;Visual_Design</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Textbook,Management</t>
+          <t>Textbook;Management</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Reference,Advanced</t>
+          <t>Reference;Advanced</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Reference,Management</t>
+          <t>Reference;Management</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Textbook,Theoretical,Advanced</t>
+          <t>Textbook;Theoretical;Advanced</t>
         </is>
       </c>
     </row>

--- a/database/supabase/templates/template_import_books.xlsx
+++ b/database/supabase/templates/template_import_books.xlsx
@@ -532,7 +532,7 @@
         <v>2018</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>850000</v>
+        <v>125000</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
         <v>2008</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>650000</v>
+        <v>110000</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -608,7 +608,7 @@
         <v>1994</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>950000</v>
+        <v>135000</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>9781119560822</t>
+          <t>9781119560821</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -646,7 +646,7 @@
         <v>2019</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>1200000</v>
+        <v>140000</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         <v>2011</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>900000</v>
+        <v>130000</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>2015</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>800000</v>
+        <v>115000</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         <v>2016</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>550000</v>
+        <v>85000</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>2017</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1100000</v>
+        <v>145000</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>2010</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1500000</v>
+        <v>150000</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>2012</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>750000</v>
+        <v>105000</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>2016</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1600000</v>
+        <v>148000</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>2012</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>700000</v>
+        <v>95000</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>2013</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1300000</v>
+        <v>138000</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>2009</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1420000</v>
+        <v>142000</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         <v>2011</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1800000</v>
+        <v>150000</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>2013</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>600000</v>
+        <v>75000</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>2015</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1150000</v>
+        <v>120000</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>2015</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>980000</v>
+        <v>118000</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>2014</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>670000</v>
+        <v>88000</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>2015</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>850000</v>
+        <v>98000</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>2016</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>930000</v>
+        <v>128000</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>2015</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>950000</v>
+        <v>132000</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>2017</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>650000</v>
+        <v>92000</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>2014</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>450000</v>
+        <v>65000</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         <v>2009</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1400000</v>
+        <v>145000</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
@@ -1598,34 +1598,34 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>9781119560822</t>
+          <t>9781119560821</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>BC9781119560822-01</t>
+          <t>BC9781119560821-01</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Kệ GEN-0822-1</t>
+          <t>Kệ GEN-0821-1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>9781119560822</t>
+          <t>9781119560821</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>BC9781119560822-02</t>
+          <t>BC9781119560821-02</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Kệ GEN-0822-2</t>
+          <t>Kệ GEN-0821-2</t>
         </is>
       </c>
     </row>
